--- a/data/trans_bre/DCD-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/DCD-Provincia-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,46; 19,99</t>
+          <t>9,31; 19,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,85; 21,76</t>
+          <t>9,82; 21,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,38; 12,17</t>
+          <t>2,75; 11,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>143,3; 823,13</t>
+          <t>151,04; 842,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>111,92; 593,41</t>
+          <t>112,46; 566,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,65; 166,28</t>
+          <t>20,94; 171,95</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,76; 12,33</t>
+          <t>4,98; 12,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 6,32</t>
+          <t>0,05; 6,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,73; 20,06</t>
+          <t>10,5; 19,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59,45; 288,16</t>
+          <t>59,11; 288,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 206,82</t>
+          <t>-0,31; 212,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,36; 221,69</t>
+          <t>71,93; 210,72</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 11,73</t>
+          <t>2,54; 11,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 12,11</t>
+          <t>3,09; 12,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,76; 16,07</t>
+          <t>5,63; 15,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29,48; 317,24</t>
+          <t>25,82; 283,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,72; 337,6</t>
+          <t>43,86; 358,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,75; 128,6</t>
+          <t>30,47; 126,99</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,72; 16,54</t>
+          <t>6,64; 16,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 14,08</t>
+          <t>3,83; 13,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 13,79</t>
+          <t>-2,13; 14,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60,25; 288,25</t>
+          <t>61,39; 301,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>37,51; 220,06</t>
+          <t>34,63; 210,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 110,61</t>
+          <t>-12,05; 115,33</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,17; 27,12</t>
+          <t>11,47; 27,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 14,82</t>
+          <t>2,28; 15,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 12,62</t>
+          <t>-3,13; 12,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60,91; 273,19</t>
+          <t>61,67; 272,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,59; 258,96</t>
+          <t>12,97; 271,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 151,81</t>
+          <t>-21,37; 157,9</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 10,95</t>
+          <t>-0,42; 11,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,9; 11,43</t>
+          <t>1,16; 11,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,86; 20,52</t>
+          <t>8,54; 20,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 132,12</t>
+          <t>-8,2; 126,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,93; 243,42</t>
+          <t>7,02; 253,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34,79; 125,74</t>
+          <t>38,8; 128,77</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,15; 13,08</t>
+          <t>6,01; 12,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 8,52</t>
+          <t>1,1; 7,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 20,83</t>
+          <t>-3,37; 21,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80,35; 272,64</t>
+          <t>80,98; 271,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,37; 135,99</t>
+          <t>11,3; 121,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,54; 133,74</t>
+          <t>-18,76; 136,93</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,32; 10,43</t>
+          <t>4,67; 10,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,68; 7,7</t>
+          <t>1,75; 7,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,44; 20,5</t>
+          <t>10,84; 21,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>65,17; 239,01</t>
+          <t>71,23; 240,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,33; 143,0</t>
+          <t>20,79; 135,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>91,63; 509,56</t>
+          <t>98,34; 505,63</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,14; 11,18</t>
+          <t>8,17; 11,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,87; 7,76</t>
+          <t>5,04; 8,16</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,5; 14,79</t>
+          <t>7,34; 14,75</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>111,66; 184,5</t>
+          <t>109,54; 185,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>67,08; 129,65</t>
+          <t>67,15; 133,07</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>62,93; 144,25</t>
+          <t>64,03; 146,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/DCD-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/DCD-Provincia-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,44</t>
+          <t>7,81</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>83,28%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,31; 19,84</t>
+          <t>8,89; 20,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,82; 21,15</t>
+          <t>9,92; 21,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,75; 11,97</t>
+          <t>3,47; 12,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>151,04; 842,04</t>
+          <t>143,29; 885,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>112,46; 566,81</t>
+          <t>112,59; 566,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,94; 171,95</t>
+          <t>29,49; 167,48</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15,66</t>
+          <t>15,08</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>135,41%</t>
+          <t>129,46%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,98; 12,88</t>
+          <t>5,01; 12,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 6,1</t>
+          <t>0,17; 6,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,5; 19,64</t>
+          <t>10,0; 19,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59,11; 288,64</t>
+          <t>60,95; 319,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 212,4</t>
+          <t>2,19; 204,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,93; 210,72</t>
+          <t>66,1; 203,23</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,84</t>
+          <t>11,08</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>74,99%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 11,64</t>
+          <t>1,81; 11,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,09; 12,13</t>
+          <t>3,06; 12,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 15,76</t>
+          <t>6,34; 16,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>25,82; 283,52</t>
+          <t>20,44; 328,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>43,86; 358,99</t>
+          <t>39,32; 353,25</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,47; 126,99</t>
+          <t>36,61; 138,19</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,83</t>
+          <t>13,55</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>102,46%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,64; 16,54</t>
+          <t>6,92; 16,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,83; 13,91</t>
+          <t>4,2; 14,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 14,37</t>
+          <t>7,84; 19,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>61,39; 301,3</t>
+          <t>66,85; 310,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,63; 210,81</t>
+          <t>39,53; 209,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 115,33</t>
+          <t>46,04; 187,56</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,27</t>
+          <t>9,95</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>106,35%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,47; 27,95</t>
+          <t>11,68; 28,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 15,6</t>
+          <t>1,46; 15,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 12,65</t>
+          <t>4,56; 15,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61,67; 272,91</t>
+          <t>64,05; 277,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,97; 271,78</t>
+          <t>5,4; 254,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 157,9</t>
+          <t>34,77; 232,19</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14,32</t>
+          <t>14,43</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>78,69%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 11,06</t>
+          <t>-0,76; 11,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 11,67</t>
+          <t>1,49; 11,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,54; 20,41</t>
+          <t>8,93; 21,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 126,02</t>
+          <t>-8,83; 137,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7,02; 253,15</t>
+          <t>7,35; 251,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>38,8; 128,77</t>
+          <t>42,35; 139,21</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11,0</t>
+          <t>20,18</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>124,75%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,01; 12,8</t>
+          <t>5,87; 12,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 7,91</t>
+          <t>0,79; 7,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 21,0</t>
+          <t>15,55; 24,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80,98; 271,02</t>
+          <t>72,23; 266,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,3; 121,82</t>
+          <t>8,28; 123,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,76; 136,93</t>
+          <t>84,1; 177,86</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14,6</t>
+          <t>11,52</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>187,23%</t>
+          <t>112,37%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,67; 10,4</t>
+          <t>4,88; 10,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,75; 7,42</t>
+          <t>1,73; 7,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,84; 21,21</t>
+          <t>8,62; 14,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71,23; 240,92</t>
+          <t>72,01; 256,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,79; 135,81</t>
+          <t>19,06; 141,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>98,34; 505,63</t>
+          <t>71,75; 164,82</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11,99</t>
+          <t>13,83</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>107,38%</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8,17; 11,22</t>
+          <t>8,13; 11,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,16</t>
+          <t>4,82; 7,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,34; 14,75</t>
+          <t>12,25; 15,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>109,54; 185,27</t>
+          <t>111,63; 186,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>67,15; 133,07</t>
+          <t>64,34; 125,05</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>64,03; 146,16</t>
+          <t>88,52; 130,46</t>
         </is>
       </c>
     </row>
